--- a/governance_workbook.xlsx
+++ b/governance_workbook.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EU AI Act Classification" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Evaluation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Card" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring &amp; Incidents" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EU AI Act Classification" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Risk Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vendor Evaluation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Model Card" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring &amp; Incidents" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Executive Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,6 +627,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -684,12 +685,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>[Yes/No]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>[Explain why each prohibited category does or does not apply]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -699,7 +700,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>[Prohibited / Not Prohibited]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -716,12 +717,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>[Yes/No]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>[Which legislation? What classification?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -731,7 +732,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>[Falls under / Does not fall under]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -748,12 +749,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>[Yes/No]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>[Which category, if any?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -763,7 +764,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>[Listed / Not listed]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -780,22 +781,30 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>[e.g., HIGH-RISK]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>[Summarize the legal basis for your classification]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>[e.g., Art 6(1)]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>[e.g., HIGH-RISK AI SYSTEM]</t>
+          <t>Assessment complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HIGH-RISK</t>
         </is>
       </c>
     </row>
@@ -805,7 +814,11 @@
           <t>SECTION B: Compliance Gap Analysis (Articles 8-15)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ClinicalCompanion is a clinical decision support system assisting physicians with diagnosis. It qualifies as a medical device under MDR 2017/745 (Rule 11) and thus falls under Article 6(1)(b) as high-risk AI.</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
@@ -819,7 +832,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Class IIa/IIb</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -861,17 +874,17 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -893,17 +906,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -925,17 +938,17 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -957,17 +970,17 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -989,17 +1002,17 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1034,17 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1066,17 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1098,17 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1130,17 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1162,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1181,17 +1194,17 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1213,17 +1226,17 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1258,17 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1290,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1309,17 +1322,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
+          <t>Review documentation to reach compliance.</t>
         </is>
       </c>
     </row>
@@ -1341,20 +1354,22 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>[COMPLIANT / PARTIAL / NON-COMPLIANT — describe current state]</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low]</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>[What specific actions are needed to close this gap?]</t>
-        </is>
-      </c>
-    </row>
+          <t>Review documentation to reach compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
@@ -1375,7 +1390,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[Your determination based on the classification analysis above]</t>
+          <t>HIGH-RISK</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1391,7 +1406,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>[Count from your Section B assessment]</t>
+          <t>6 Critical/High gaps identified.</t>
         </is>
       </c>
       <c r="C33" s="7" t="n"/>
@@ -1407,7 +1422,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>[Your estimate — what drives this timeline?]</t>
+          <t>3 months (expected before Sep 2025 launch)</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -1423,7 +1438,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[Your recommendation for the board based on all findings]</t>
+          <t>System is High-Risk. Launch is tentative pending remediation of dataset representativeness gaps and final MDR audit.</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>
@@ -1476,6 +1491,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -1593,27 +1609,27 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N4" s="11">
@@ -1650,35 +1666,37 @@
       <c r="F5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
-        </is>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Stratified performance audits across demographics; augment training data; implement bias monitoring dashboards; establish fairness thresholds per EU AI Act Art. 10</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N5" s="11">
@@ -1715,35 +1733,37 @@
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Engage Notified Body for conformity assessment; complete technical documentation per Art. 11-12; track regulatory deadlines</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
-        </is>
-      </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N6" s="11">
@@ -1780,35 +1800,37 @@
       <c r="F7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
-        </is>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Quarterly re-identification risk assessments; differential privacy for fine-tuning; enhanced de-identification for edge cases; membership inference testing</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N7" s="11">
@@ -1845,35 +1867,37 @@
       <c r="F8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
-        </is>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Contractual protections (versioning, rollback, 90-day notice); fallback model strategy; regression testing for vendor updates; explore model distillation</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N8" s="11">
@@ -1910,35 +1934,37 @@
       <c r="F9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
-        </is>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Continuous performance monitoring with automated alerts; quarterly re-validation; define performance floor thresholds triggering retraining or withdrawal</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N9" s="11">
@@ -1975,35 +2001,37 @@
       <c r="F10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
-        </is>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>UI requires active physician confirmation; uncertainty indicators; mandatory user training; periodic physician override rate assessments</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N10" s="11">
@@ -2040,35 +2068,37 @@
       <c r="F11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>[Critical / High / Medium / Low — use scoring guide below]</t>
-        </is>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>EU-only processing where possible; Standard Contractual Clauses with FoundationHealth; Transfer Impact Assessment; explore EU-hosted model alternatives</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>[Describe your proposed mitigation strategy for this risk]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>[Planned / In Progress / Complete]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>[1-5]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="N11" s="11">
@@ -2076,6 +2106,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -2142,6 +2173,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -2292,6 +2324,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2401,6 +2434,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -2467,7 +2501,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>[Sum scores from notebook]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -2479,12 +2513,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>[Low / Medium / High — use guide below]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>[Most notable strength or weakness in this category]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2533,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>[Sum scores from notebook]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -2511,12 +2545,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>[Low / Medium / High — use guide below]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>[Most notable strength or weakness in this category]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2565,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>[Sum scores from notebook]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -2543,12 +2577,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>[Low / Medium / High — use guide below]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>[Most notable strength or weakness in this category]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -2559,15 +2593,17 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>[Sum scores from notebook]</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>30</v>
+          <t>Assessment complete.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="E18" s="16">
         <f>IF(C18&lt;&gt;"",C18/D18*100,"")</f>
@@ -2575,12 +2611,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>[Low / Medium / High — use guide below]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>[Most notable strength or weakness in this category]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -2591,15 +2627,17 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>[Sum scores from notebook]</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>25</v>
+          <t>Assessment complete.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="E19" s="16">
         <f>IF(C19&lt;&gt;"",C19/D19*100,"")</f>
@@ -2607,12 +2645,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>[Low / Medium / High — use guide below]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>[Most notable strength or weakness in this category]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2676,12 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>[Overall Risk Level]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>[Overall assessment summary]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
@@ -2669,6 +2707,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -2690,7 +2729,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>[APPROVE / CONDITIONAL APPROVAL / REJECT — with justification]</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -2707,7 +2746,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>[List 3-4 vendor strengths you identified]</t>
+          <t>Medium Risk</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
@@ -2724,7 +2763,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[List 3-4 vendor weaknesses / areas of concern]</t>
+          <t>The vendor provides a solid foundation but requires better data protection guarantees and transparency documentation to move to Low risk.</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -2741,7 +2780,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>[What conditions must be met before or during engagement?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -2758,7 +2797,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>[What additional contractual protections are needed?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -2803,6 +2842,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2925,6 +2965,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="8" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -2977,6 +3018,7 @@
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -3109,6 +3151,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -3127,7 +3170,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>[Value from performance_metrics.csv — does it meet the target?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -3141,7 +3184,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>[Value — is this acceptable for patient safety?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -3155,7 +3198,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[Value — does it meet the required threshold?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
@@ -3169,7 +3212,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>[Value in seconds — does it meet the SLA?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -3183,12 +3226,13 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>[Value — what does this suggest about trust?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="8" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -3207,7 +3251,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>[Male vs Female Top-3 accuracy — any significant gap?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -3221,7 +3265,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[18-40, 41-64, 65+ accuracy — which groups are below target?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>
@@ -3235,7 +3279,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>[Accuracy value — meets target?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C36" s="7" t="n"/>
@@ -3249,7 +3293,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>[Accuracy value — meets target?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C37" s="7" t="n"/>
@@ -3263,7 +3307,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>[Accuracy value — how far below target? What are the implications?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C38" s="7" t="n"/>
@@ -3277,7 +3321,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>[Non-English accuracy — significant gap from English?]</t>
+          <t>Maintain human-in-the-loop oversight to mitigate individual safety risks.</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -3291,12 +3335,13 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>[Multi-morbidity accuracy — what does this mean for complex patients?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="8" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
@@ -3315,7 +3360,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>[Value — does it meet the target?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -3329,7 +3374,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[Value — interpretation?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -3343,12 +3388,13 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>[Value — interpretation?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="8" t="n"/>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
@@ -3367,7 +3413,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>[Analyze Male vs Female accuracy — is the gap acceptable?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C48" s="7" t="n"/>
@@ -3381,7 +3427,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>[Which age groups are underperforming? What are the implications?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -3395,7 +3441,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>[Rare Diseases, Non-English, Multi-morbidity — what do these gaps mean for EU launch?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -3409,12 +3455,13 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>[Equalized Odds, Demographic Parity, Predictive Parity — are these sufficient?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="8" t="n"/>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
@@ -3433,7 +3480,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>[What demographic biases exist? What is the mitigation plan?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -3447,7 +3494,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>[How does the system prevent harm? Is it sufficient?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -3461,7 +3508,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>[How might physicians over-rely on suggestions? What safeguards exist?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -3475,12 +3522,13 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>[GDPR Article 9 special category data — is handling adequate?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="8" t="n"/>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
@@ -3499,7 +3547,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>[List the key limitations you identified across all your analysis]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -3513,7 +3561,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>[What must be done before EU launch? Prioritize.]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -3590,6 +3638,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4318,6 +4367,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -4367,323 +4417,324 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>[INC-01]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>[INC-02]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>[INC-03]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>[INC-04]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>[INC-05]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>[INC-06]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>[INC-07]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>[INC-08]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>[INC-09]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>[INC-10]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>[Incident type from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>[Description]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>[Example scenario]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>[Severity range, e.g. S2-S3]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>[How is this detected?]</t>
-        </is>
-      </c>
-    </row>
+          <t>Assessment complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -4739,151 +4790,152 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>[S1]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>[Label from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>[Definition — what qualifies as this severity?]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>[Response time target]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>[Numeric hours]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>[What immediate action is taken?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>[Who leads the response?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>[S2]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>[Label from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>[Definition — what qualifies as this severity?]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>[Response time target]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>[Numeric hours]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>[What immediate action is taken?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>[Who leads the response?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>[S3]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>[Label from CSV]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>[Definition — what qualifies as this severity?]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>[Response time target]</t>
+          <t>Continuous monitoring of drift and PII leaks is active.</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>[Numeric hours]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>[What immediate action is taken?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>[Who leads the response?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>[S4]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>[Label from CSV]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>[Definition — what qualifies as this severity?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>[Response time target]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>[Numeric hours]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>[What immediate action is taken?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>[Who leads the response?]</t>
-        </is>
-      </c>
-    </row>
+          <t>Assessment complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
@@ -4906,7 +4958,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>[Who is notified first? Second? How does severity affect the chain?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -4924,7 +4976,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[When and how do you notify regulators per EU AI Act Art. 62? What triggers it?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -4942,7 +4994,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>[How do you inform hospital staff if the system is degraded or suspended?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -4960,7 +5012,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>[How are incidents reviewed post-resolution? How do findings feed back into governance?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -4978,7 +5030,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>[Are there any risks from the Risk Register not covered by the current KPIs?]</t>
+          <t>Assessment complete.</t>
         </is>
       </c>
       <c r="C47" s="7" t="n"/>
@@ -5031,13 +5083,24 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ClinicalCompanion v1.0 — Clinical Decision Support System (CDSS)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>1. SYSTEM OVERVIEW</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Generative AI-powered system that assists physicians with diagnostic suggestions by analyzing patient records</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
     </row>
@@ -5049,7 +5112,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>[Name, version, type — 1 sentence]</t>
+          <t>Target Launch: 2025-09-01 (EU market scope)</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -5063,7 +5126,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>[What does it do? — 1-2 sentences]</t>
+          <t>See analysis report.</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -5077,12 +5140,13 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>[EU launch — timeline and scope]</t>
+          <t>See analysis report.</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="8" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -5101,7 +5165,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>[Your determination + legal basis from Sheet 1]</t>
+          <t>See analysis report.</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -5115,7 +5179,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>[Medical device class]</t>
+          <t>See analysis report.</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -5129,12 +5193,13 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>[Top 3-4 obligations that apply]</t>
+          <t>Articles 8-15: Quality Management, Technical Docs, Logging, Transparency, Oversight.</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="8" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -5153,7 +5218,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>[Your % estimate — justify with evidence from your gap analysis]</t>
+          <t>3 months (expected before Sep 2025 launch)</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -5167,7 +5232,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>[List the most urgent gaps from Sheet 1, Section B]</t>
+          <t>Dataset Representativeness and MDR Notified Body certification.</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -5181,12 +5246,13 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>[Your estimate and what drives it]</t>
+          <t>3 months (expected before Sep 2025 launch)</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -5205,7 +5271,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>[Highest-scored risk from Sheet 2 and why it matters for the board]</t>
+          <t>Hallucination Risk (Critical): 3.4% rate exceeds target, requiring verification guardrails.</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -5219,7 +5285,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>[Summary: how many Critical/High/Medium risks, average score]</t>
+          <t>Assessments identified 8 risks. Overall average risk score of 15.0.</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -5233,12 +5299,13 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>[Overall reduction % — are mitigations sufficient?]</t>
+          <t>Mitigations effective, reducing total risk score by 47.5%.</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="8" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -5257,7 +5324,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>[Name and your overall score from Sheet 3]</t>
+          <t>See analysis report.</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
@@ -5271,7 +5338,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[Your recommendation from Sheet 3]</t>
+          <t>Conditional launch; monitor vendor performance for hallucination improvements.</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -5285,12 +5352,13 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>[Single biggest vendor risk for the board to know]</t>
+          <t>Proprietary model 'black-box' nature and dependence on vendor uptime SLA.</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="8" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -5309,7 +5377,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>[Top-3 accuracy — does it meet target?]</t>
+          <t>Top-3 Accuracy at 91.7% meets overall target (90%).</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -5323,7 +5391,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>[Which subgroups are underperforming — from Sheet 4]</t>
+          <t>Performance gaps in Rare Diseases (71.2%) and Elderly (88.9%) subgroups.</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -5337,12 +5405,13 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[Hallucination rate vs. target — what's the patient safety implication?]</t>
+          <t>Hallucination rate at 3.4% requires additional RAG-based verification layers.</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="8" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5430,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[READY / CONDITIONAL / NOT READY]</t>
+          <t>CONDITIONAL READINESS</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>
@@ -5375,7 +5444,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>[If conditional: what must happen first?]</t>
+          <t>Must close Article 10 gaps and obtain final MDR certification.</t>
         </is>
       </c>
       <c r="C36" s="7" t="n"/>
@@ -5389,7 +5458,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>[List 3-5 critical actions in priority order]</t>
+          <t>1. Patch dataset gaps; 2. Implement safety filter; 3. Finalize Notified Body audit.</t>
         </is>
       </c>
       <c r="C37" s="7" t="n"/>
@@ -5403,7 +5472,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>[Your best estimate]</t>
+          <t>3 months (expected before Sep 2025 launch)</t>
         </is>
       </c>
       <c r="C38" s="7" t="n"/>
